--- a/Fase 1 planificacion/Evidencias Proyecto/Evidencias de documentacion/Roadmap del proyecto.xlsx
+++ b/Fase 1 planificacion/Evidencias Proyecto/Evidencias de documentacion/Roadmap del proyecto.xlsx
@@ -16,18 +16,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
-  <si>
-    <t>Hoja de ruta del producto</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>&lt;Simutech&gt;</t>
-  </si>
-  <si>
-    <t>MES 1</t>
-  </si>
-  <si>
-    <t>MES 2</t>
   </si>
   <si>
     <t>S1</t>
@@ -84,15 +75,6 @@
     <t>S18</t>
   </si>
   <si>
-    <t>SPRINT REVIEW 1</t>
-  </si>
-  <si>
-    <t>SPRINT REVIEW 2</t>
-  </si>
-  <si>
-    <t>SPRINT REVIEW 3</t>
-  </si>
-  <si>
     <t>SPRINT 1</t>
   </si>
   <si>
@@ -106,7 +88,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <sz val="12.0"/>
       <color theme="1"/>
@@ -140,8 +122,18 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="14.0"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <sz val="13.0"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color theme="0"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -178,26 +170,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFF00"/>
+        <fgColor theme="4"/>
+        <bgColor theme="4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFF2CC"/>
+        <fgColor theme="6"/>
+        <bgColor theme="6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB6DDE8"/>
-        <bgColor rgb="FFB6DDE8"/>
+        <fgColor theme="5"/>
+        <bgColor theme="5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor rgb="FF92D050"/>
+        <fgColor rgb="FF0B5394"/>
+        <bgColor rgb="FF0B5394"/>
       </patternFill>
     </fill>
     <fill>
@@ -363,24 +355,21 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
     <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="2" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="5" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf borderId="6" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf borderId="7" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
@@ -402,14 +391,8 @@
     <xf borderId="13" fillId="8" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="13" fillId="9" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="13" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="14" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf borderId="14" fillId="9" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="15" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="16" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -419,7 +402,13 @@
     <xf borderId="17" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="18" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="19" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="17" fillId="11" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="17" fillId="11" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="14" fillId="10" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf borderId="14" fillId="8" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -435,11 +424,11 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>133350</xdr:colOff>
+      <xdr:colOff>123825</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="5657850" cy="733425"/>
+    <xdr:ext cx="3895725" cy="752475"/>
     <xdr:sp>
       <xdr:nvSpPr>
         <xdr:cNvPr id="3" name="Shape 3"/>
@@ -447,8 +436,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4607831" y="3622863"/>
-          <a:ext cx="2157900" cy="647400"/>
+          <a:off x="2517075" y="3413288"/>
+          <a:ext cx="5657850" cy="733425"/>
         </a:xfrm>
         <a:prstGeom prst="homePlate">
           <a:avLst>
@@ -483,7 +472,7 @@
             <a:buNone/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="en-US" sz="1100">
+            <a:rPr lang="en-US" sz="1500">
               <a:solidFill>
                 <a:schemeClr val="lt1"/>
               </a:solidFill>
@@ -492,45 +481,9 @@
               <a:cs typeface="Calibri"/>
               <a:sym typeface="Calibri"/>
             </a:rPr>
-            <a:t>Documentación</a:t>
+            <a:t>Documentación, planificación del proyecto, estructura del sistema.</a:t>
           </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="Calibri"/>
-              <a:ea typeface="Calibri"/>
-              <a:cs typeface="Calibri"/>
-              <a:sym typeface="Calibri"/>
-            </a:rPr>
-            <a:t>, </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="Calibri"/>
-              <a:ea typeface="Calibri"/>
-              <a:cs typeface="Calibri"/>
-              <a:sym typeface="Calibri"/>
-            </a:rPr>
-            <a:t>planificación</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="Calibri"/>
-              <a:ea typeface="Calibri"/>
-              <a:cs typeface="Calibri"/>
-              <a:sym typeface="Calibri"/>
-            </a:rPr>
-            <a:t> del proyecto, estructura del sistema.</a:t>
-          </a:r>
-          <a:endParaRPr sz="1100">
+          <a:endParaRPr sz="1500">
             <a:solidFill>
               <a:schemeClr val="lt1"/>
             </a:solidFill>
@@ -558,7 +511,1065 @@
           <a:r>
             <a:t/>
           </a:r>
-          <a:endParaRPr sz="1100">
+          <a:endParaRPr sz="1500">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Calibri"/>
+            <a:ea typeface="Calibri"/>
+            <a:cs typeface="Calibri"/>
+            <a:sym typeface="Calibri"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="7677150" cy="752475"/>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="2" name="Shape 2" title="Dibujo"/>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="294375" y="1071750"/>
+          <a:ext cx="8138125" cy="945300"/>
+          <a:chOff x="294375" y="1071750"/>
+          <a:chExt cx="8138125" cy="945300"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp>
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="4" name="Shape 4"/>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="294375" y="1071750"/>
+            <a:ext cx="2225400" cy="945300"/>
+          </a:xfrm>
+          <a:prstGeom prst="homePlate">
+            <a:avLst>
+              <a:gd fmla="val 50000" name="adj"/>
+            </a:avLst>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="accent3"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:txBody>
+          <a:bodyPr anchorCtr="0" anchor="t" bIns="45700" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="45700">
+            <a:noAutofit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+              <a:spcBef>
+                <a:spcPts val="0"/>
+              </a:spcBef>
+              <a:spcAft>
+                <a:spcPts val="0"/>
+              </a:spcAft>
+              <a:buClr>
+                <a:schemeClr val="lt1"/>
+              </a:buClr>
+              <a:buSzPts val="1100"/>
+              <a:buFont typeface="Calibri"/>
+              <a:buNone/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1800">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+                <a:ea typeface="Calibri"/>
+                <a:cs typeface="Calibri"/>
+                <a:sym typeface="Calibri"/>
+              </a:rPr>
+              <a:t>Vista principal de Empresas.</a:t>
+            </a:r>
+            <a:endParaRPr sz="1800">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+              <a:ea typeface="Calibri"/>
+              <a:cs typeface="Calibri"/>
+              <a:sym typeface="Calibri"/>
+            </a:endParaRPr>
+          </a:p>
+          <a:p>
+            <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+              <a:spcBef>
+                <a:spcPts val="0"/>
+              </a:spcBef>
+              <a:spcAft>
+                <a:spcPts val="0"/>
+              </a:spcAft>
+              <a:buClr>
+                <a:schemeClr val="lt1"/>
+              </a:buClr>
+              <a:buSzPts val="1100"/>
+              <a:buFont typeface="Calibri"/>
+              <a:buNone/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="1800">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+              <a:ea typeface="Calibri"/>
+              <a:cs typeface="Calibri"/>
+              <a:sym typeface="Calibri"/>
+            </a:endParaRPr>
+          </a:p>
+          <a:p>
+            <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+              <a:spcBef>
+                <a:spcPts val="0"/>
+              </a:spcBef>
+              <a:spcAft>
+                <a:spcPts val="0"/>
+              </a:spcAft>
+              <a:buClr>
+                <a:schemeClr val="lt1"/>
+              </a:buClr>
+              <a:buSzPts val="1100"/>
+              <a:buFont typeface="Calibri"/>
+              <a:buNone/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+              <a:ea typeface="Calibri"/>
+              <a:cs typeface="Calibri"/>
+              <a:sym typeface="Calibri"/>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp>
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="5" name="Shape 5"/>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="2765100" y="1071750"/>
+            <a:ext cx="2424000" cy="945300"/>
+          </a:xfrm>
+          <a:prstGeom prst="homePlate">
+            <a:avLst>
+              <a:gd fmla="val 50000" name="adj"/>
+            </a:avLst>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="accent3"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:txBody>
+          <a:bodyPr anchorCtr="0" anchor="t" bIns="45700" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="45700">
+            <a:noAutofit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+              <a:spcBef>
+                <a:spcPts val="0"/>
+              </a:spcBef>
+              <a:spcAft>
+                <a:spcPts val="0"/>
+              </a:spcAft>
+              <a:buClr>
+                <a:schemeClr val="lt1"/>
+              </a:buClr>
+              <a:buSzPts val="1100"/>
+              <a:buFont typeface="Calibri"/>
+              <a:buNone/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1800">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+                <a:ea typeface="Calibri"/>
+                <a:cs typeface="Calibri"/>
+                <a:sym typeface="Calibri"/>
+              </a:rPr>
+              <a:t>Funcionalidades clave del portal Postulaciones</a:t>
+            </a:r>
+            <a:endParaRPr sz="1800">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+              <a:ea typeface="Calibri"/>
+              <a:cs typeface="Calibri"/>
+              <a:sym typeface="Calibri"/>
+            </a:endParaRPr>
+          </a:p>
+          <a:p>
+            <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+              <a:spcBef>
+                <a:spcPts val="0"/>
+              </a:spcBef>
+              <a:spcAft>
+                <a:spcPts val="0"/>
+              </a:spcAft>
+              <a:buClr>
+                <a:schemeClr val="lt1"/>
+              </a:buClr>
+              <a:buSzPts val="1100"/>
+              <a:buFont typeface="Calibri"/>
+              <a:buNone/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="1800">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+              <a:ea typeface="Calibri"/>
+              <a:cs typeface="Calibri"/>
+              <a:sym typeface="Calibri"/>
+            </a:endParaRPr>
+          </a:p>
+          <a:p>
+            <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+              <a:spcBef>
+                <a:spcPts val="0"/>
+              </a:spcBef>
+              <a:spcAft>
+                <a:spcPts val="0"/>
+              </a:spcAft>
+              <a:buClr>
+                <a:schemeClr val="lt1"/>
+              </a:buClr>
+              <a:buSzPts val="1100"/>
+              <a:buFont typeface="Calibri"/>
+              <a:buNone/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+              <a:ea typeface="Calibri"/>
+              <a:cs typeface="Calibri"/>
+              <a:sym typeface="Calibri"/>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp>
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="6" name="Shape 6"/>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="5324200" y="1071750"/>
+            <a:ext cx="3108300" cy="945300"/>
+          </a:xfrm>
+          <a:prstGeom prst="homePlate">
+            <a:avLst>
+              <a:gd fmla="val 50000" name="adj"/>
+            </a:avLst>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="accent3"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:txBody>
+          <a:bodyPr anchorCtr="0" anchor="t" bIns="45700" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="45700">
+            <a:noAutofit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+              <a:spcBef>
+                <a:spcPts val="0"/>
+              </a:spcBef>
+              <a:spcAft>
+                <a:spcPts val="0"/>
+              </a:spcAft>
+              <a:buClr>
+                <a:schemeClr val="lt1"/>
+              </a:buClr>
+              <a:buSzPts val="1100"/>
+              <a:buFont typeface="Calibri"/>
+              <a:buNone/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1800">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+                <a:ea typeface="Calibri"/>
+                <a:cs typeface="Calibri"/>
+                <a:sym typeface="Calibri"/>
+              </a:rPr>
+              <a:t>Implementación</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" sz="1800">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+                <a:ea typeface="Calibri"/>
+                <a:cs typeface="Calibri"/>
+                <a:sym typeface="Calibri"/>
+              </a:rPr>
+              <a:t> de mejoras</a:t>
+            </a:r>
+            <a:endParaRPr sz="1800">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+              <a:ea typeface="Calibri"/>
+              <a:cs typeface="Calibri"/>
+              <a:sym typeface="Calibri"/>
+            </a:endParaRPr>
+          </a:p>
+          <a:p>
+            <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+              <a:spcBef>
+                <a:spcPts val="0"/>
+              </a:spcBef>
+              <a:spcAft>
+                <a:spcPts val="0"/>
+              </a:spcAft>
+              <a:buClr>
+                <a:schemeClr val="lt1"/>
+              </a:buClr>
+              <a:buSzPts val="1100"/>
+              <a:buFont typeface="Calibri"/>
+              <a:buNone/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="1800">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+              <a:ea typeface="Calibri"/>
+              <a:cs typeface="Calibri"/>
+              <a:sym typeface="Calibri"/>
+            </a:endParaRPr>
+          </a:p>
+          <a:p>
+            <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+              <a:spcBef>
+                <a:spcPts val="0"/>
+              </a:spcBef>
+              <a:spcAft>
+                <a:spcPts val="0"/>
+              </a:spcAft>
+              <a:buClr>
+                <a:schemeClr val="lt1"/>
+              </a:buClr>
+              <a:buSzPts val="1100"/>
+              <a:buFont typeface="Calibri"/>
+              <a:buNone/>
+            </a:pPr>
+            <a:r>
+              <a:t/>
+            </a:r>
+            <a:endParaRPr sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+              <a:ea typeface="Calibri"/>
+              <a:cs typeface="Calibri"/>
+              <a:sym typeface="Calibri"/>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>723900</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4752975" cy="990600"/>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="2" name="Shape 2" title="Dibujo"/>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="152400" y="152400"/>
+          <a:ext cx="4631700" cy="967925"/>
+          <a:chOff x="152400" y="152400"/>
+          <a:chExt cx="4631700" cy="967925"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp>
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="7" name="Shape 7"/>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="463525" y="362825"/>
+            <a:ext cx="2080800" cy="757500"/>
+          </a:xfrm>
+          <a:prstGeom prst="homePlate">
+            <a:avLst>
+              <a:gd fmla="val 50000" name="adj"/>
+            </a:avLst>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="accent3"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:txBody>
+          <a:bodyPr anchorCtr="0" anchor="t" bIns="45700" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="45700">
+            <a:noAutofit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+              <a:spcBef>
+                <a:spcPts val="0"/>
+              </a:spcBef>
+              <a:spcAft>
+                <a:spcPts val="0"/>
+              </a:spcAft>
+              <a:buClr>
+                <a:schemeClr val="lt1"/>
+              </a:buClr>
+              <a:buSzPts val="1100"/>
+              <a:buFont typeface="Calibri"/>
+              <a:buNone/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1300">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+                <a:ea typeface="Calibri"/>
+                <a:cs typeface="Calibri"/>
+                <a:sym typeface="Calibri"/>
+              </a:rPr>
+              <a:t> Vista principal de postulantes + login/register</a:t>
+            </a:r>
+            <a:endParaRPr sz="1300">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+              <a:ea typeface="Calibri"/>
+              <a:cs typeface="Calibri"/>
+              <a:sym typeface="Calibri"/>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp>
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="8" name="Shape 8"/>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="2703300" y="362825"/>
+            <a:ext cx="2080800" cy="757500"/>
+          </a:xfrm>
+          <a:prstGeom prst="homePlate">
+            <a:avLst>
+              <a:gd fmla="val 50000" name="adj"/>
+            </a:avLst>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="accent3"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:txBody>
+          <a:bodyPr anchorCtr="0" anchor="t" bIns="45700" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="45700">
+            <a:noAutofit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+              <a:spcBef>
+                <a:spcPts val="0"/>
+              </a:spcBef>
+              <a:spcAft>
+                <a:spcPts val="0"/>
+              </a:spcAft>
+              <a:buClr>
+                <a:schemeClr val="lt1"/>
+              </a:buClr>
+              <a:buSzPts val="1100"/>
+              <a:buFont typeface="Calibri"/>
+              <a:buNone/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1300">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+                <a:ea typeface="Calibri"/>
+                <a:cs typeface="Calibri"/>
+                <a:sym typeface="Calibri"/>
+              </a:rPr>
+              <a:t>Funciones clave del portal postulantes</a:t>
+            </a:r>
+            <a:endParaRPr sz="1300">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+              <a:ea typeface="Calibri"/>
+              <a:cs typeface="Calibri"/>
+              <a:sym typeface="Calibri"/>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp>
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="9" name="Shape 9"/>
+          <xdr:cNvSpPr txBox="1"/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="152400" y="152400"/>
+            <a:ext cx="3000000" cy="384900"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:txBody>
+          <a:bodyPr anchorCtr="0" anchor="t" bIns="91425" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="91425">
+            <a:spAutoFit/>
+          </a:bodyPr>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+              <a:spcBef>
+                <a:spcPts val="0"/>
+              </a:spcBef>
+              <a:spcAft>
+                <a:spcPts val="0"/>
+              </a:spcAft>
+              <a:buNone/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1300">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="Calibri"/>
+                <a:ea typeface="Calibri"/>
+                <a:cs typeface="Calibri"/>
+                <a:sym typeface="Calibri"/>
+              </a:rPr>
+              <a:t>s</a:t>
+            </a:r>
+            <a:endParaRPr sz="1400"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>304800</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2752725" cy="790575"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="11" name="Shape 11"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="-51450" y="103500"/>
+          <a:ext cx="2100300" cy="772800"/>
+        </a:xfrm>
+        <a:prstGeom prst="homePlate">
+          <a:avLst>
+            <a:gd fmla="val 50000" name="adj"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="93C47D"/>
+        </a:solidFill>
+        <a:ln cap="flat" cmpd="sng" w="9525">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd len="sm" w="sm" type="none"/>
+          <a:tailEnd len="sm" w="sm" type="none"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr anchorCtr="0" anchor="ctr" bIns="91425" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="91425">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Creación</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> de la nube + host de aplicaciones</a:t>
+          </a:r>
+          <a:endParaRPr sz="1400">
+            <a:solidFill>
+              <a:srgbClr val="FFFFFF"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>2009775</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>1190625</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2295525" cy="657225"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="Shape 12"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3574450" y="2679300"/>
+          <a:ext cx="2763900" cy="634200"/>
+        </a:xfrm>
+        <a:prstGeom prst="homePlate">
+          <a:avLst>
+            <a:gd fmla="val 50000" name="adj"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="93C47D"/>
+        </a:solidFill>
+        <a:ln cap="flat" cmpd="sng" w="9525">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd len="sm" w="sm" type="none"/>
+          <a:tailEnd len="sm" w="sm" type="none"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr anchorCtr="0" anchor="ctr" bIns="91425" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="91425">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="ctr">
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Implementación</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> de la BD + Conexion con la nube</a:t>
+          </a:r>
+          <a:endParaRPr sz="1400">
+            <a:solidFill>
+              <a:srgbClr val="FFFFFF"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1962150" cy="647700"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="Shape 13"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="255650" y="242225"/>
+          <a:ext cx="2357700" cy="624000"/>
+        </a:xfrm>
+        <a:prstGeom prst="homePlate">
+          <a:avLst>
+            <a:gd fmla="val 50000" name="adj"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="93C47D"/>
+        </a:solidFill>
+        <a:ln cap="flat" cmpd="sng" w="9525">
+          <a:solidFill>
+            <a:srgbClr val="FFFFFF"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd len="sm" w="sm" type="none"/>
+          <a:tailEnd len="sm" w="sm" type="none"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr anchorCtr="0" anchor="ctr" bIns="91425" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="91425">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="ctr">
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Vista de </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>capacitador</a:t>
+          </a:r>
+          <a:endParaRPr sz="1400">
+            <a:solidFill>
+              <a:srgbClr val="FFFFFF"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1819275" cy="342900"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="Shape 14"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2517075" y="3413300"/>
+          <a:ext cx="2738100" cy="411900"/>
+        </a:xfrm>
+        <a:prstGeom prst="homePlate">
+          <a:avLst>
+            <a:gd fmla="val 50000" name="adj"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="366092"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr anchorCtr="0" anchor="t" bIns="45700" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="45700">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClr>
+              <a:schemeClr val="lt1"/>
+            </a:buClr>
+            <a:buSzPts val="1100"/>
+            <a:buFont typeface="Calibri"/>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1500">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+              <a:ea typeface="Calibri"/>
+              <a:cs typeface="Calibri"/>
+              <a:sym typeface="Calibri"/>
+            </a:rPr>
+            <a:t>Visión</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1500">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+              <a:ea typeface="Calibri"/>
+              <a:cs typeface="Calibri"/>
+              <a:sym typeface="Calibri"/>
+            </a:rPr>
+            <a:t> y resumen del proyecto</a:t>
+          </a:r>
+          <a:endParaRPr sz="1500">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Calibri"/>
+            <a:ea typeface="Calibri"/>
+            <a:cs typeface="Calibri"/>
+            <a:sym typeface="Calibri"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClr>
+              <a:schemeClr val="lt1"/>
+            </a:buClr>
+            <a:buSzPts val="1100"/>
+            <a:buFont typeface="Calibri"/>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr sz="1500">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Calibri"/>
+            <a:ea typeface="Calibri"/>
+            <a:cs typeface="Calibri"/>
+            <a:sym typeface="Calibri"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1076325</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1085850" cy="342900"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="Shape 15"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2517075" y="3413294"/>
+          <a:ext cx="1349700" cy="392100"/>
+        </a:xfrm>
+        <a:prstGeom prst="homePlate">
+          <a:avLst>
+            <a:gd fmla="val 50000" name="adj"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="366092"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr anchorCtr="0" anchor="t" bIns="45700" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="45700">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClr>
+              <a:schemeClr val="lt1"/>
+            </a:buClr>
+            <a:buSzPts val="1100"/>
+            <a:buFont typeface="Calibri"/>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1500">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+              <a:ea typeface="Calibri"/>
+              <a:cs typeface="Calibri"/>
+              <a:sym typeface="Calibri"/>
+            </a:rPr>
+            <a:t>Caso de Uso</a:t>
+          </a:r>
+          <a:endParaRPr sz="1500">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Calibri"/>
+            <a:ea typeface="Calibri"/>
+            <a:cs typeface="Calibri"/>
+            <a:sym typeface="Calibri"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClr>
+              <a:schemeClr val="lt1"/>
+            </a:buClr>
+            <a:buSzPts val="1100"/>
+            <a:buFont typeface="Calibri"/>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr sz="1500">
             <a:solidFill>
               <a:schemeClr val="lt1"/>
             </a:solidFill>
@@ -575,20 +1586,1333 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>66675</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="7877175" cy="781050"/>
+    <xdr:ext cx="866775" cy="342900"/>
     <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="Shape 4"/>
+        <xdr:cNvPr id="16" name="Shape 16"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4464952" y="3651432"/>
-          <a:ext cx="2109900" cy="414000"/>
+          <a:off x="2517075" y="3413294"/>
+          <a:ext cx="1042200" cy="352500"/>
+        </a:xfrm>
+        <a:prstGeom prst="homePlate">
+          <a:avLst>
+            <a:gd fmla="val 50000" name="adj"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="366092"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr anchorCtr="0" anchor="t" bIns="45700" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="45700">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClr>
+              <a:schemeClr val="lt1"/>
+            </a:buClr>
+            <a:buSzPts val="1100"/>
+            <a:buFont typeface="Calibri"/>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1500">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+              <a:ea typeface="Calibri"/>
+              <a:cs typeface="Calibri"/>
+              <a:sym typeface="Calibri"/>
+            </a:rPr>
+            <a:t>Mockup</a:t>
+          </a:r>
+          <a:endParaRPr sz="1500">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Calibri"/>
+            <a:ea typeface="Calibri"/>
+            <a:cs typeface="Calibri"/>
+            <a:sym typeface="Calibri"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClr>
+              <a:schemeClr val="lt1"/>
+            </a:buClr>
+            <a:buSzPts val="1100"/>
+            <a:buFont typeface="Calibri"/>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr sz="1500">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Calibri"/>
+            <a:ea typeface="Calibri"/>
+            <a:cs typeface="Calibri"/>
+            <a:sym typeface="Calibri"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1819275" cy="342900"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="Shape 17"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2517075" y="3413294"/>
+          <a:ext cx="1677000" cy="342600"/>
+        </a:xfrm>
+        <a:prstGeom prst="homePlate">
+          <a:avLst>
+            <a:gd fmla="val 50000" name="adj"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="366092"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr anchorCtr="0" anchor="t" bIns="45700" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="45700">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClr>
+              <a:schemeClr val="lt1"/>
+            </a:buClr>
+            <a:buSzPts val="1100"/>
+            <a:buFont typeface="Calibri"/>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1500">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+              <a:ea typeface="Calibri"/>
+              <a:cs typeface="Calibri"/>
+              <a:sym typeface="Calibri"/>
+            </a:rPr>
+            <a:t>Modelo de datos</a:t>
+          </a:r>
+          <a:endParaRPr sz="1500">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Calibri"/>
+            <a:ea typeface="Calibri"/>
+            <a:cs typeface="Calibri"/>
+            <a:sym typeface="Calibri"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClr>
+              <a:schemeClr val="lt1"/>
+            </a:buClr>
+            <a:buSzPts val="1100"/>
+            <a:buFont typeface="Calibri"/>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr sz="1500">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Calibri"/>
+            <a:ea typeface="Calibri"/>
+            <a:cs typeface="Calibri"/>
+            <a:sym typeface="Calibri"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1819275" cy="342900"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="Shape 18"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2517075" y="3413294"/>
+          <a:ext cx="764700" cy="352500"/>
+        </a:xfrm>
+        <a:prstGeom prst="homePlate">
+          <a:avLst>
+            <a:gd fmla="val 50000" name="adj"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="366092"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr anchorCtr="0" anchor="t" bIns="45700" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="45700">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClr>
+              <a:schemeClr val="lt1"/>
+            </a:buClr>
+            <a:buSzPts val="1100"/>
+            <a:buFont typeface="Calibri"/>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1700">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+              <a:ea typeface="Calibri"/>
+              <a:cs typeface="Calibri"/>
+              <a:sym typeface="Calibri"/>
+            </a:rPr>
+            <a:t>Gantt</a:t>
+          </a:r>
+          <a:endParaRPr sz="1700">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Calibri"/>
+            <a:ea typeface="Calibri"/>
+            <a:cs typeface="Calibri"/>
+            <a:sym typeface="Calibri"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClr>
+              <a:schemeClr val="lt1"/>
+            </a:buClr>
+            <a:buSzPts val="1100"/>
+            <a:buFont typeface="Calibri"/>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr sz="1700">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Calibri"/>
+            <a:ea typeface="Calibri"/>
+            <a:cs typeface="Calibri"/>
+            <a:sym typeface="Calibri"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1962150" cy="600075"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="Shape 19"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1742325" y="1498200"/>
+          <a:ext cx="2097900" cy="941100"/>
+        </a:xfrm>
+        <a:prstGeom prst="homePlate">
+          <a:avLst>
+            <a:gd fmla="val 50000" name="adj"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="6AA84F"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr anchorCtr="0" anchor="t" bIns="45700" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="45700">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClr>
+              <a:schemeClr val="lt1"/>
+            </a:buClr>
+            <a:buSzPts val="1100"/>
+            <a:buFont typeface="Calibri"/>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1800">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+              <a:ea typeface="Calibri"/>
+              <a:cs typeface="Calibri"/>
+              <a:sym typeface="Calibri"/>
+            </a:rPr>
+            <a:t>Módulo</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1800">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+              <a:ea typeface="Calibri"/>
+              <a:cs typeface="Calibri"/>
+              <a:sym typeface="Calibri"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1800">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+              <a:ea typeface="Calibri"/>
+              <a:cs typeface="Calibri"/>
+              <a:sym typeface="Calibri"/>
+            </a:rPr>
+            <a:t>Generación</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1800">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+              <a:ea typeface="Calibri"/>
+              <a:cs typeface="Calibri"/>
+              <a:sym typeface="Calibri"/>
+            </a:rPr>
+            <a:t> de oferta laboral.</a:t>
+          </a:r>
+          <a:endParaRPr sz="1800">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Calibri"/>
+            <a:ea typeface="Calibri"/>
+            <a:cs typeface="Calibri"/>
+            <a:sym typeface="Calibri"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClr>
+              <a:schemeClr val="lt1"/>
+            </a:buClr>
+            <a:buSzPts val="1100"/>
+            <a:buFont typeface="Calibri"/>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr sz="1800">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Calibri"/>
+            <a:ea typeface="Calibri"/>
+            <a:cs typeface="Calibri"/>
+            <a:sym typeface="Calibri"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClr>
+              <a:schemeClr val="lt1"/>
+            </a:buClr>
+            <a:buSzPts val="1100"/>
+            <a:buFont typeface="Calibri"/>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Calibri"/>
+            <a:ea typeface="Calibri"/>
+            <a:cs typeface="Calibri"/>
+            <a:sym typeface="Calibri"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>762000</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1819275" cy="561975"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="Shape 20"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1742325" y="1498200"/>
+          <a:ext cx="1750200" cy="703500"/>
+        </a:xfrm>
+        <a:prstGeom prst="homePlate">
+          <a:avLst>
+            <a:gd fmla="val 50000" name="adj"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="6AA84F"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr anchorCtr="0" anchor="t" bIns="45700" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="45700">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClr>
+              <a:schemeClr val="lt1"/>
+            </a:buClr>
+            <a:buSzPts val="1100"/>
+            <a:buFont typeface="Calibri"/>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1800">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+              <a:ea typeface="Calibri"/>
+              <a:cs typeface="Calibri"/>
+              <a:sym typeface="Calibri"/>
+            </a:rPr>
+            <a:t>Modulo Enviar </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1800">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+              <a:ea typeface="Calibri"/>
+              <a:cs typeface="Calibri"/>
+              <a:sym typeface="Calibri"/>
+            </a:rPr>
+            <a:t>Postulación</a:t>
+          </a:r>
+          <a:endParaRPr sz="1800">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Calibri"/>
+            <a:ea typeface="Calibri"/>
+            <a:cs typeface="Calibri"/>
+            <a:sym typeface="Calibri"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClr>
+              <a:schemeClr val="lt1"/>
+            </a:buClr>
+            <a:buSzPts val="1100"/>
+            <a:buFont typeface="Calibri"/>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr sz="1800">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Calibri"/>
+            <a:ea typeface="Calibri"/>
+            <a:cs typeface="Calibri"/>
+            <a:sym typeface="Calibri"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClr>
+              <a:schemeClr val="lt1"/>
+            </a:buClr>
+            <a:buSzPts val="1100"/>
+            <a:buFont typeface="Calibri"/>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Calibri"/>
+            <a:ea typeface="Calibri"/>
+            <a:cs typeface="Calibri"/>
+            <a:sym typeface="Calibri"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1876425" cy="657225"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="Shape 21"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1802375" y="1518225"/>
+          <a:ext cx="1880100" cy="993600"/>
+        </a:xfrm>
+        <a:prstGeom prst="homePlate">
+          <a:avLst>
+            <a:gd fmla="val 50000" name="adj"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="6AA84F"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr anchorCtr="0" anchor="t" bIns="45700" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="45700">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClr>
+              <a:schemeClr val="lt1"/>
+            </a:buClr>
+            <a:buSzPts val="1100"/>
+            <a:buFont typeface="Calibri"/>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1800">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+              <a:ea typeface="Calibri"/>
+              <a:cs typeface="Calibri"/>
+              <a:sym typeface="Calibri"/>
+            </a:rPr>
+            <a:t>Modulo </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1800">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+              <a:ea typeface="Calibri"/>
+              <a:cs typeface="Calibri"/>
+              <a:sym typeface="Calibri"/>
+            </a:rPr>
+            <a:t>calificación</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1800">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+              <a:ea typeface="Calibri"/>
+              <a:cs typeface="Calibri"/>
+              <a:sym typeface="Calibri"/>
+            </a:rPr>
+            <a:t> del practicante</a:t>
+          </a:r>
+          <a:endParaRPr sz="1800">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Calibri"/>
+            <a:ea typeface="Calibri"/>
+            <a:cs typeface="Calibri"/>
+            <a:sym typeface="Calibri"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClr>
+              <a:schemeClr val="lt1"/>
+            </a:buClr>
+            <a:buSzPts val="1100"/>
+            <a:buFont typeface="Calibri"/>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr sz="1800">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Calibri"/>
+            <a:ea typeface="Calibri"/>
+            <a:cs typeface="Calibri"/>
+            <a:sym typeface="Calibri"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClr>
+              <a:schemeClr val="lt1"/>
+            </a:buClr>
+            <a:buSzPts val="1100"/>
+            <a:buFont typeface="Calibri"/>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Calibri"/>
+            <a:ea typeface="Calibri"/>
+            <a:cs typeface="Calibri"/>
+            <a:sym typeface="Calibri"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>19050</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>1457325</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2143125" cy="542925"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="22" name="Shape 22"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2252975" y="1343525"/>
+          <a:ext cx="1759800" cy="527700"/>
+        </a:xfrm>
+        <a:prstGeom prst="homePlate">
+          <a:avLst>
+            <a:gd fmla="val 50000" name="adj"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="93C47D"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr anchorCtr="0" anchor="t" bIns="45700" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="45700">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClr>
+              <a:schemeClr val="lt1"/>
+            </a:buClr>
+            <a:buSzPts val="1100"/>
+            <a:buFont typeface="Calibri"/>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1300">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+              <a:ea typeface="Calibri"/>
+              <a:cs typeface="Calibri"/>
+              <a:sym typeface="Calibri"/>
+            </a:rPr>
+            <a:t>Vista SuperAdmin</a:t>
+          </a:r>
+          <a:endParaRPr sz="1300">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Calibri"/>
+            <a:ea typeface="Calibri"/>
+            <a:cs typeface="Calibri"/>
+            <a:sym typeface="Calibri"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>266700</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>1419225</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1819275" cy="561975"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="23" name="Shape 23"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1742325" y="1498200"/>
+          <a:ext cx="1750200" cy="703500"/>
+        </a:xfrm>
+        <a:prstGeom prst="homePlate">
+          <a:avLst>
+            <a:gd fmla="val 50000" name="adj"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="6AA84F"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr anchorCtr="0" anchor="t" bIns="45700" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="45700">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClr>
+              <a:schemeClr val="lt1"/>
+            </a:buClr>
+            <a:buSzPts val="1100"/>
+            <a:buFont typeface="Calibri"/>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1800">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+              <a:ea typeface="Calibri"/>
+              <a:cs typeface="Calibri"/>
+              <a:sym typeface="Calibri"/>
+            </a:rPr>
+            <a:t>Control total del sistema</a:t>
+          </a:r>
+          <a:endParaRPr sz="1800">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Calibri"/>
+            <a:ea typeface="Calibri"/>
+            <a:cs typeface="Calibri"/>
+            <a:sym typeface="Calibri"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClr>
+              <a:schemeClr val="lt1"/>
+            </a:buClr>
+            <a:buSzPts val="1100"/>
+            <a:buFont typeface="Calibri"/>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr sz="1800">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Calibri"/>
+            <a:ea typeface="Calibri"/>
+            <a:cs typeface="Calibri"/>
+            <a:sym typeface="Calibri"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClr>
+              <a:schemeClr val="lt1"/>
+            </a:buClr>
+            <a:buSzPts val="1100"/>
+            <a:buFont typeface="Calibri"/>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Calibri"/>
+            <a:ea typeface="Calibri"/>
+            <a:cs typeface="Calibri"/>
+            <a:sym typeface="Calibri"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>1514475</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>523875</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3124200" cy="752475"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="24" name="Shape 24"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2792400" y="1642150"/>
+          <a:ext cx="3108300" cy="945300"/>
+        </a:xfrm>
+        <a:prstGeom prst="homePlate">
+          <a:avLst>
+            <a:gd fmla="val 50000" name="adj"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="93C47D"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr anchorCtr="0" anchor="t" bIns="45700" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="45700">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClr>
+              <a:schemeClr val="lt1"/>
+            </a:buClr>
+            <a:buSzPts val="1100"/>
+            <a:buFont typeface="Calibri"/>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1800">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+              <a:ea typeface="Calibri"/>
+              <a:cs typeface="Calibri"/>
+              <a:sym typeface="Calibri"/>
+            </a:rPr>
+            <a:t>Adaptación</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1800">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+              <a:ea typeface="Calibri"/>
+              <a:cs typeface="Calibri"/>
+              <a:sym typeface="Calibri"/>
+            </a:rPr>
+            <a:t> responsive</a:t>
+          </a:r>
+          <a:endParaRPr sz="1800">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Calibri"/>
+            <a:ea typeface="Calibri"/>
+            <a:cs typeface="Calibri"/>
+            <a:sym typeface="Calibri"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClr>
+              <a:schemeClr val="lt1"/>
+            </a:buClr>
+            <a:buSzPts val="1100"/>
+            <a:buFont typeface="Calibri"/>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1800">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+              <a:ea typeface="Calibri"/>
+              <a:cs typeface="Calibri"/>
+              <a:sym typeface="Calibri"/>
+            </a:rPr>
+            <a:t>Web.</a:t>
+          </a:r>
+          <a:endParaRPr sz="1800">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Calibri"/>
+            <a:ea typeface="Calibri"/>
+            <a:cs typeface="Calibri"/>
+            <a:sym typeface="Calibri"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClr>
+              <a:schemeClr val="lt1"/>
+            </a:buClr>
+            <a:buSzPts val="1100"/>
+            <a:buFont typeface="Calibri"/>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr sz="1800">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Calibri"/>
+            <a:ea typeface="Calibri"/>
+            <a:cs typeface="Calibri"/>
+            <a:sym typeface="Calibri"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClr>
+              <a:schemeClr val="lt1"/>
+            </a:buClr>
+            <a:buSzPts val="1100"/>
+            <a:buFont typeface="Calibri"/>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Calibri"/>
+            <a:ea typeface="Calibri"/>
+            <a:cs typeface="Calibri"/>
+            <a:sym typeface="Calibri"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>1514475</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="2752725" cy="647700"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="25" name="Shape 25"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2792400" y="1642150"/>
+          <a:ext cx="2731500" cy="739500"/>
+        </a:xfrm>
+        <a:prstGeom prst="homePlate">
+          <a:avLst>
+            <a:gd fmla="val 50000" name="adj"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="93C47D"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr anchorCtr="0" anchor="t" bIns="45700" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="45700">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClr>
+              <a:schemeClr val="lt1"/>
+            </a:buClr>
+            <a:buSzPts val="1100"/>
+            <a:buFont typeface="Calibri"/>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1800">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+              <a:ea typeface="Calibri"/>
+              <a:cs typeface="Calibri"/>
+              <a:sym typeface="Calibri"/>
+            </a:rPr>
+            <a:t>Implementación</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1800">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+              <a:ea typeface="Calibri"/>
+              <a:cs typeface="Calibri"/>
+              <a:sym typeface="Calibri"/>
+            </a:rPr>
+            <a:t> de Vistas responsive</a:t>
+          </a:r>
+          <a:endParaRPr sz="1800">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Calibri"/>
+            <a:ea typeface="Calibri"/>
+            <a:cs typeface="Calibri"/>
+            <a:sym typeface="Calibri"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClr>
+              <a:schemeClr val="lt1"/>
+            </a:buClr>
+            <a:buSzPts val="1100"/>
+            <a:buFont typeface="Calibri"/>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr sz="1800">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Calibri"/>
+            <a:ea typeface="Calibri"/>
+            <a:cs typeface="Calibri"/>
+            <a:sym typeface="Calibri"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClr>
+              <a:schemeClr val="lt1"/>
+            </a:buClr>
+            <a:buSzPts val="1100"/>
+            <a:buFont typeface="Calibri"/>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Calibri"/>
+            <a:ea typeface="Calibri"/>
+            <a:cs typeface="Calibri"/>
+            <a:sym typeface="Calibri"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData fLocksWithSheet="0"/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>1885950</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="1876425" cy="781050"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="26" name="Shape 26"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2465925" y="2342650"/>
+          <a:ext cx="1316700" cy="429300"/>
         </a:xfrm>
         <a:prstGeom prst="homePlate">
           <a:avLst>
@@ -632,7 +2956,7 @@
               <a:cs typeface="Calibri"/>
               <a:sym typeface="Calibri"/>
             </a:rPr>
-            <a:t>Desarrollo Web</a:t>
+            <a:t>Pruebas</a:t>
           </a:r>
           <a:endParaRPr sz="1800">
             <a:solidFill>
@@ -688,7 +3012,16 @@
             <a:buNone/>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:rPr lang="en-US" sz="1100">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+              <a:ea typeface="Calibri"/>
+              <a:cs typeface="Calibri"/>
+              <a:sym typeface="Calibri"/>
+            </a:rPr>
+            <a:t>D</a:t>
           </a:r>
           <a:endParaRPr sz="1100">
             <a:solidFill>
@@ -706,21 +3039,21 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>1504950</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>1885950</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="4810125" cy="676275"/>
+    <xdr:ext cx="1819275" cy="495300"/>
     <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="Shape 5"/>
+        <xdr:cNvPr id="27" name="Shape 27"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4460175" y="3687125"/>
-          <a:ext cx="2157000" cy="660000"/>
+          <a:off x="294375" y="1071750"/>
+          <a:ext cx="2225400" cy="659400"/>
         </a:xfrm>
         <a:prstGeom prst="homePlate">
           <a:avLst>
@@ -740,7 +3073,7 @@
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="ctr">
+          <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
             <a:spcBef>
               <a:spcPts val="0"/>
             </a:spcBef>
@@ -755,7 +3088,7 @@
             <a:buNone/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="en-US" sz="1300">
+            <a:rPr lang="en-US" sz="1800">
               <a:solidFill>
                 <a:schemeClr val="lt1"/>
               </a:solidFill>
@@ -764,49 +3097,18 @@
               <a:cs typeface="Calibri"/>
               <a:sym typeface="Calibri"/>
             </a:rPr>
-            <a:t>Desarrollo aplicacion movil</a:t>
+            <a:t>Pruebas de compatibilidad</a:t>
           </a:r>
-          <a:endParaRPr sz="1600"/>
+          <a:endParaRPr sz="1800">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Calibri"/>
+            <a:ea typeface="Calibri"/>
+            <a:cs typeface="Calibri"/>
+            <a:sym typeface="Calibri"/>
+          </a:endParaRPr>
         </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData fLocksWithSheet="0"/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>914400</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="2085975" cy="400050"/>
-    <xdr:sp>
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="Shape 6"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4312538" y="3594263"/>
-          <a:ext cx="2066925" cy="371475"/>
-        </a:xfrm>
-        <a:prstGeom prst="homePlate">
-          <a:avLst>
-            <a:gd fmla="val 50000" name="adj"/>
-          </a:avLst>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="E69138"/>
-        </a:solidFill>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr anchorCtr="0" anchor="t" bIns="45700" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="45700">
-          <a:noAutofit/>
-        </a:bodyPr>
-        <a:lstStyle/>
         <a:p>
           <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
             <a:spcBef>
@@ -823,18 +3125,9 @@
             <a:buNone/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="en-US" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="lt1"/>
-              </a:solidFill>
-              <a:latin typeface="Calibri"/>
-              <a:ea typeface="Calibri"/>
-              <a:cs typeface="Calibri"/>
-              <a:sym typeface="Calibri"/>
-            </a:rPr>
-            <a:t>Ajustes finales</a:t>
+            <a:t/>
           </a:r>
-          <a:endParaRPr sz="1100">
+          <a:endParaRPr sz="1800">
             <a:solidFill>
               <a:schemeClr val="lt1"/>
             </a:solidFill>
@@ -879,20 +3172,20 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>914400</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:colOff>1885950</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="1981200" cy="400050"/>
+    <xdr:ext cx="1771650" cy="438150"/>
     <xdr:sp>
       <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="Shape 7"/>
+        <xdr:cNvPr id="28" name="Shape 28"/>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4226825" y="3594276"/>
-          <a:ext cx="1965600" cy="375600"/>
+          <a:off x="294375" y="1071750"/>
+          <a:ext cx="2225400" cy="489300"/>
         </a:xfrm>
         <a:prstGeom prst="homePlate">
           <a:avLst>
@@ -900,7 +3193,7 @@
           </a:avLst>
         </a:prstGeom>
         <a:solidFill>
-          <a:srgbClr val="E69138"/>
+          <a:schemeClr val="accent3"/>
         </a:solidFill>
         <a:ln>
           <a:noFill/>
@@ -927,7 +3220,7 @@
             <a:buNone/>
           </a:pPr>
           <a:r>
-            <a:rPr lang="en-US" sz="1100">
+            <a:rPr lang="en-US" sz="1800">
               <a:solidFill>
                 <a:schemeClr val="lt1"/>
               </a:solidFill>
@@ -936,9 +3229,101 @@
               <a:cs typeface="Calibri"/>
               <a:sym typeface="Calibri"/>
             </a:rPr>
-            <a:t>Migración del Sistema a Producción</a:t>
+            <a:t>Implementacion</a:t>
           </a:r>
-          <a:endParaRPr sz="1400"/>
+          <a:endParaRPr sz="1800">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Calibri"/>
+            <a:ea typeface="Calibri"/>
+            <a:cs typeface="Calibri"/>
+            <a:sym typeface="Calibri"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClr>
+              <a:schemeClr val="lt1"/>
+            </a:buClr>
+            <a:buSzPts val="1100"/>
+            <a:buFont typeface="Calibri"/>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr sz="1800">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Calibri"/>
+            <a:ea typeface="Calibri"/>
+            <a:cs typeface="Calibri"/>
+            <a:sym typeface="Calibri"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClr>
+              <a:schemeClr val="lt1"/>
+            </a:buClr>
+            <a:buSzPts val="1100"/>
+            <a:buFont typeface="Calibri"/>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr sz="1800">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Calibri"/>
+            <a:ea typeface="Calibri"/>
+            <a:cs typeface="Calibri"/>
+            <a:sym typeface="Calibri"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClr>
+              <a:schemeClr val="lt1"/>
+            </a:buClr>
+            <a:buSzPts val="1100"/>
+            <a:buFont typeface="Calibri"/>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Calibri"/>
+            <a:ea typeface="Calibri"/>
+            <a:cs typeface="Calibri"/>
+            <a:sym typeface="Calibri"/>
+          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -946,385 +3331,398 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>809625</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>1885950</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2028825" cy="981075"/>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="8" name="Shape 8" title="Dibujo"/>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
+    <xdr:ext cx="1819275" cy="495300"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="29" name="Shape 29"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
         <a:xfrm>
-          <a:off x="960675" y="1260900"/>
-          <a:ext cx="2391600" cy="960600"/>
-          <a:chOff x="960675" y="1260900"/>
-          <a:chExt cx="2391600" cy="960600"/>
+          <a:off x="294375" y="1071750"/>
+          <a:ext cx="2225400" cy="659400"/>
         </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:sp>
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="9" name="Shape 9"/>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="960675" y="1260900"/>
-            <a:ext cx="2391600" cy="960600"/>
-          </a:xfrm>
-          <a:prstGeom prst="rightArrow">
-            <a:avLst>
-              <a:gd fmla="val 50000" name="adj1"/>
-              <a:gd fmla="val 50000" name="adj2"/>
-            </a:avLst>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="CFE2F3"/>
-          </a:solidFill>
-          <a:ln cap="flat" cmpd="sng" w="9525">
+        <a:prstGeom prst="homePlate">
+          <a:avLst>
+            <a:gd fmla="val 50000" name="adj"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent3"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr anchorCtr="0" anchor="t" bIns="45700" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="45700">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClr>
+              <a:schemeClr val="lt1"/>
+            </a:buClr>
+            <a:buSzPts val="1100"/>
+            <a:buFont typeface="Calibri"/>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1800">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+              <a:ea typeface="Calibri"/>
+              <a:cs typeface="Calibri"/>
+              <a:sym typeface="Calibri"/>
+            </a:rPr>
+            <a:t>Pruebas de rendimiento</a:t>
+          </a:r>
+          <a:endParaRPr sz="1800">
             <a:solidFill>
-              <a:srgbClr val="000000"/>
+              <a:schemeClr val="lt1"/>
             </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="sm" w="sm" type="none"/>
-            <a:tailEnd len="sm" w="sm" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:txBody>
-          <a:bodyPr anchorCtr="0" anchor="ctr" bIns="91425" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="91425">
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="ctr">
-              <a:spcBef>
-                <a:spcPts val="0"/>
-              </a:spcBef>
-              <a:spcAft>
-                <a:spcPts val="0"/>
-              </a:spcAft>
-              <a:buNone/>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr sz="1400"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp>
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="10" name="Shape 10"/>
-          <xdr:cNvSpPr txBox="1"/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="1230900" y="1596150"/>
-            <a:ext cx="1681200" cy="290100"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:txBody>
-          <a:bodyPr anchorCtr="0" anchor="t" bIns="91425" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="91425">
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
-              <a:spcBef>
-                <a:spcPts val="0"/>
-              </a:spcBef>
-              <a:spcAft>
-                <a:spcPts val="0"/>
-              </a:spcAft>
-              <a:buNone/>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" sz="1400"/>
-              <a:t>Fase de Pruebas</a:t>
-            </a:r>
-            <a:endParaRPr sz="1400"/>
-          </a:p>
-          <a:p>
-            <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
-              <a:spcBef>
-                <a:spcPts val="0"/>
-              </a:spcBef>
-              <a:spcAft>
-                <a:spcPts val="0"/>
-              </a:spcAft>
-              <a:buNone/>
-            </a:pPr>
-            <a:r>
-              <a:t/>
-            </a:r>
-            <a:endParaRPr sz="1400"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
+            <a:latin typeface="Calibri"/>
+            <a:ea typeface="Calibri"/>
+            <a:cs typeface="Calibri"/>
+            <a:sym typeface="Calibri"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClr>
+              <a:schemeClr val="lt1"/>
+            </a:buClr>
+            <a:buSzPts val="1100"/>
+            <a:buFont typeface="Calibri"/>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr sz="1800">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Calibri"/>
+            <a:ea typeface="Calibri"/>
+            <a:cs typeface="Calibri"/>
+            <a:sym typeface="Calibri"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClr>
+              <a:schemeClr val="lt1"/>
+            </a:buClr>
+            <a:buSzPts val="1100"/>
+            <a:buFont typeface="Calibri"/>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Calibri"/>
+            <a:ea typeface="Calibri"/>
+            <a:cs typeface="Calibri"/>
+            <a:sym typeface="Calibri"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData fLocksWithSheet="0"/>
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>781050</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>590550</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="2381250" cy="1171575"/>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="8" name="Shape 8" title="Dibujo"/>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
+    <xdr:ext cx="2057400" cy="542925"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="30" name="Shape 30"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
         <a:xfrm>
-          <a:off x="3122975" y="2060000"/>
-          <a:ext cx="3580200" cy="1749200"/>
-          <a:chOff x="3122975" y="2060000"/>
-          <a:chExt cx="3580200" cy="1749200"/>
+          <a:off x="324400" y="1081750"/>
+          <a:ext cx="2225400" cy="659400"/>
         </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:sp>
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="11" name="Shape 11"/>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="3122975" y="2060000"/>
-            <a:ext cx="3580200" cy="803400"/>
-          </a:xfrm>
-          <a:prstGeom prst="homePlate">
-            <a:avLst>
-              <a:gd fmla="val 50000" name="adj"/>
-            </a:avLst>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="F6B26B"/>
-          </a:solidFill>
-          <a:ln cap="flat" cmpd="sng" w="9525">
+        <a:prstGeom prst="homePlate">
+          <a:avLst>
+            <a:gd fmla="val 50000" name="adj"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent3"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr anchorCtr="0" anchor="t" bIns="45700" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="45700">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClr>
+              <a:schemeClr val="lt1"/>
+            </a:buClr>
+            <a:buSzPts val="1100"/>
+            <a:buFont typeface="Calibri"/>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1800">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+              <a:ea typeface="Calibri"/>
+              <a:cs typeface="Calibri"/>
+              <a:sym typeface="Calibri"/>
+            </a:rPr>
+            <a:t>Cierre del projecto</a:t>
+          </a:r>
+          <a:endParaRPr sz="1800">
             <a:solidFill>
-              <a:srgbClr val="000000"/>
+              <a:schemeClr val="lt1"/>
             </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="sm" w="sm" type="none"/>
-            <a:tailEnd len="sm" w="sm" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:txBody>
-          <a:bodyPr anchorCtr="0" anchor="ctr" bIns="91425" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="91425">
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="ctr">
-              <a:spcBef>
-                <a:spcPts val="0"/>
-              </a:spcBef>
-              <a:spcAft>
-                <a:spcPts val="0"/>
-              </a:spcAft>
-              <a:buNone/>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" sz="1400"/>
-              <a:t>Cierre del proyecto</a:t>
-            </a:r>
-            <a:endParaRPr sz="1400"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp>
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="12" name="Shape 12"/>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="3122975" y="3005800"/>
-            <a:ext cx="3580200" cy="803400"/>
-          </a:xfrm>
-          <a:prstGeom prst="homePlate">
-            <a:avLst>
-              <a:gd fmla="val 50000" name="adj"/>
-            </a:avLst>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="F6B26B"/>
-          </a:solidFill>
-          <a:ln cap="flat" cmpd="sng" w="9525">
+            <a:latin typeface="Calibri"/>
+            <a:ea typeface="Calibri"/>
+            <a:cs typeface="Calibri"/>
+            <a:sym typeface="Calibri"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClr>
+              <a:schemeClr val="lt1"/>
+            </a:buClr>
+            <a:buSzPts val="1100"/>
+            <a:buFont typeface="Calibri"/>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr sz="1800">
             <a:solidFill>
-              <a:srgbClr val="000000"/>
+              <a:schemeClr val="lt1"/>
             </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="sm" w="sm" type="none"/>
-            <a:tailEnd len="sm" w="sm" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:txBody>
-          <a:bodyPr anchorCtr="0" anchor="ctr" bIns="91425" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="91425">
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="ctr">
-              <a:spcBef>
-                <a:spcPts val="0"/>
-              </a:spcBef>
-              <a:spcAft>
-                <a:spcPts val="0"/>
-              </a:spcAft>
-              <a:buNone/>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" sz="1400"/>
-              <a:t>Entrega</a:t>
-            </a:r>
-            <a:endParaRPr sz="1400"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
+            <a:latin typeface="Calibri"/>
+            <a:ea typeface="Calibri"/>
+            <a:cs typeface="Calibri"/>
+            <a:sym typeface="Calibri"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClr>
+              <a:schemeClr val="lt1"/>
+            </a:buClr>
+            <a:buSzPts val="1100"/>
+            <a:buFont typeface="Calibri"/>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Calibri"/>
+            <a:ea typeface="Calibri"/>
+            <a:cs typeface="Calibri"/>
+            <a:sym typeface="Calibri"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData fLocksWithSheet="0"/>
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>781050</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>1190625</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="6334125" cy="2000250"/>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="8" name="Shape 8" title="Dibujo"/>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
+    <xdr:ext cx="2057400" cy="542925"/>
+    <xdr:sp>
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="31" name="Shape 31"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
         <a:xfrm>
-          <a:off x="4560975" y="2192575"/>
-          <a:ext cx="5117400" cy="1979775"/>
-          <a:chOff x="4560975" y="2192575"/>
-          <a:chExt cx="5117400" cy="1979775"/>
+          <a:off x="294375" y="1071750"/>
+          <a:ext cx="2225400" cy="659400"/>
         </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:sp>
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="13" name="Shape 13"/>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="7119675" y="3269950"/>
-            <a:ext cx="2558700" cy="902400"/>
-          </a:xfrm>
-          <a:prstGeom prst="homePlate">
-            <a:avLst>
-              <a:gd fmla="val 50000" name="adj"/>
-            </a:avLst>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="B6D7A8"/>
-          </a:solidFill>
-          <a:ln cap="flat" cmpd="sng" w="9525">
+        <a:prstGeom prst="homePlate">
+          <a:avLst>
+            <a:gd fmla="val 50000" name="adj"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent3"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr anchorCtr="0" anchor="t" bIns="45700" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="45700">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClr>
+              <a:schemeClr val="lt1"/>
+            </a:buClr>
+            <a:buSzPts val="1100"/>
+            <a:buFont typeface="Calibri"/>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1800">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri"/>
+              <a:ea typeface="Calibri"/>
+              <a:cs typeface="Calibri"/>
+              <a:sym typeface="Calibri"/>
+            </a:rPr>
+            <a:t>Entrega Final</a:t>
+          </a:r>
+          <a:endParaRPr sz="1800">
             <a:solidFill>
-              <a:srgbClr val="000000"/>
+              <a:schemeClr val="lt1"/>
             </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="sm" w="sm" type="none"/>
-            <a:tailEnd len="sm" w="sm" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:txBody>
-          <a:bodyPr anchorCtr="0" anchor="ctr" bIns="91425" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="91425">
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="ctr">
-              <a:spcBef>
-                <a:spcPts val="0"/>
-              </a:spcBef>
-              <a:spcAft>
-                <a:spcPts val="0"/>
-              </a:spcAft>
-              <a:buNone/>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" sz="1400"/>
-              <a:t>Backend</a:t>
-            </a:r>
-            <a:endParaRPr sz="1400"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-      <xdr:sp>
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="14" name="Shape 14"/>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="4560975" y="2192575"/>
-            <a:ext cx="2558700" cy="902400"/>
-          </a:xfrm>
-          <a:prstGeom prst="homePlate">
-            <a:avLst>
-              <a:gd fmla="val 50000" name="adj"/>
-            </a:avLst>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="B6D7A8"/>
-          </a:solidFill>
-          <a:ln cap="flat" cmpd="sng" w="9525">
+            <a:latin typeface="Calibri"/>
+            <a:ea typeface="Calibri"/>
+            <a:cs typeface="Calibri"/>
+            <a:sym typeface="Calibri"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClr>
+              <a:schemeClr val="lt1"/>
+            </a:buClr>
+            <a:buSzPts val="1100"/>
+            <a:buFont typeface="Calibri"/>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr sz="1800">
             <a:solidFill>
-              <a:srgbClr val="000000"/>
+              <a:schemeClr val="lt1"/>
             </a:solidFill>
-            <a:prstDash val="solid"/>
-            <a:round/>
-            <a:headEnd len="sm" w="sm" type="none"/>
-            <a:tailEnd len="sm" w="sm" type="none"/>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:txBody>
-          <a:bodyPr anchorCtr="0" anchor="ctr" bIns="91425" lIns="91425" spcFirstLastPara="1" rIns="91425" wrap="square" tIns="91425">
-            <a:noAutofit/>
-          </a:bodyPr>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="ctr">
-              <a:spcBef>
-                <a:spcPts val="0"/>
-              </a:spcBef>
-              <a:spcAft>
-                <a:spcPts val="0"/>
-              </a:spcAft>
-              <a:buNone/>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" sz="1400"/>
-              <a:t>Front end</a:t>
-            </a:r>
-            <a:endParaRPr sz="1400"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
+            <a:latin typeface="Calibri"/>
+            <a:ea typeface="Calibri"/>
+            <a:cs typeface="Calibri"/>
+            <a:sym typeface="Calibri"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr indent="0" lvl="0" marL="0" rtl="0" algn="l">
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClr>
+              <a:schemeClr val="lt1"/>
+            </a:buClr>
+            <a:buSzPts val="1100"/>
+            <a:buFont typeface="Calibri"/>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:t/>
+          </a:r>
+          <a:endParaRPr sz="1100">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="Calibri"/>
+            <a:ea typeface="Calibri"/>
+            <a:cs typeface="Calibri"/>
+            <a:sym typeface="Calibri"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData fLocksWithSheet="0"/>
   </xdr:oneCellAnchor>
 </xdr:wsDr>
@@ -1531,16 +3929,23 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="4" max="4" width="18.0"/>
-    <col customWidth="1" min="5" max="5" width="17.44"/>
-    <col customWidth="1" min="6" max="6" width="16.0"/>
-    <col customWidth="1" min="7" max="7" width="16.67"/>
-    <col customWidth="1" min="8" max="8" width="19.44"/>
-    <col customWidth="1" min="9" max="9" width="20.11"/>
-    <col customWidth="1" min="10" max="10" width="19.0"/>
-    <col customWidth="1" min="11" max="11" width="19.44"/>
-    <col customWidth="1" min="12" max="12" width="22.33"/>
-    <col customWidth="1" min="21" max="21" width="18.44"/>
+    <col customWidth="1" min="4" max="4" width="10.11"/>
+    <col customWidth="1" min="5" max="5" width="12.78"/>
+    <col customWidth="1" min="6" max="6" width="11.56"/>
+    <col customWidth="1" min="7" max="7" width="12.22"/>
+    <col customWidth="1" min="8" max="8" width="25.0"/>
+    <col customWidth="1" min="9" max="9" width="29.56"/>
+    <col customWidth="1" min="10" max="10" width="18.56"/>
+    <col customWidth="1" min="11" max="11" width="18.0"/>
+    <col customWidth="1" min="12" max="12" width="12.33"/>
+    <col customWidth="1" min="13" max="13" width="13.89"/>
+    <col customWidth="1" min="14" max="14" width="10.78"/>
+    <col customWidth="1" min="15" max="15" width="10.56"/>
+    <col customWidth="1" min="16" max="16" width="23.89"/>
+    <col customWidth="1" min="17" max="17" width="22.33"/>
+    <col customWidth="1" min="18" max="18" width="12.44"/>
+    <col customWidth="1" min="19" max="19" width="9.44"/>
+    <col customWidth="1" min="21" max="21" width="12.89"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
@@ -1589,9 +3994,7 @@
       <c r="AD2" s="1"/>
     </row>
     <row r="3" ht="24.75" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>0</v>
-      </c>
+      <c r="A3" s="2"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
@@ -1688,32 +4091,28 @@
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="5"/>
-      <c r="D6" s="6" t="s">
-        <v>2</v>
-      </c>
+      <c r="D6" s="6"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
-      <c r="H6" s="8" t="s">
-        <v>3</v>
-      </c>
+      <c r="H6" s="6"/>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
       <c r="K6" s="7"/>
-      <c r="L6" s="9"/>
-      <c r="M6" s="9"/>
-      <c r="N6" s="9"/>
-      <c r="O6" s="9"/>
-      <c r="P6" s="9"/>
-      <c r="Q6" s="9"/>
-      <c r="R6" s="9"/>
-      <c r="S6" s="9"/>
-      <c r="T6" s="9"/>
-      <c r="U6" s="9"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="8"/>
+      <c r="N6" s="8"/>
+      <c r="O6" s="8"/>
+      <c r="P6" s="8"/>
+      <c r="Q6" s="8"/>
+      <c r="R6" s="8"/>
+      <c r="S6" s="8"/>
+      <c r="T6" s="8"/>
+      <c r="U6" s="8"/>
       <c r="V6" s="1"/>
       <c r="W6" s="1"/>
       <c r="X6" s="1"/>
@@ -1725,62 +4124,62 @@
       <c r="AD6" s="1"/>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="10"/>
-      <c r="B7" s="11"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="13" t="s">
+      <c r="A7" s="9"/>
+      <c r="B7" s="10"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="G7" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="H7" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="I7" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="G7" s="13" t="s">
+      <c r="J7" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H7" s="13" t="s">
+      <c r="K7" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="I7" s="13" t="s">
+      <c r="L7" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="J7" s="13" t="s">
+      <c r="M7" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="K7" s="13" t="s">
+      <c r="N7" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="L7" s="13" t="s">
+      <c r="O7" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="M7" s="13" t="s">
+      <c r="P7" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="N7" s="13" t="s">
+      <c r="Q7" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="O7" s="13" t="s">
+      <c r="R7" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="P7" s="13" t="s">
+      <c r="S7" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="Q7" s="13" t="s">
+      <c r="T7" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="R7" s="13" t="s">
+      <c r="U7" s="12" t="s">
         <v>18</v>
-      </c>
-      <c r="S7" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="T7" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="U7" s="13" t="s">
-        <v>21</v>
       </c>
       <c r="V7" s="1"/>
       <c r="W7" s="1"/>
@@ -1793,33 +4192,27 @@
       <c r="AD7" s="1"/>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="14"/>
-      <c r="B8" s="14"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="15"/>
-      <c r="E8" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" s="16"/>
-      <c r="G8" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="H8" s="17"/>
-      <c r="I8" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="J8" s="19"/>
-      <c r="K8" s="19"/>
-      <c r="L8" s="19"/>
+      <c r="A8" s="13"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="15"/>
       <c r="M8" s="15"/>
       <c r="N8" s="15"/>
       <c r="O8" s="15"/>
-      <c r="P8" s="17"/>
-      <c r="Q8" s="17"/>
-      <c r="R8" s="18"/>
-      <c r="S8" s="19"/>
-      <c r="T8" s="19"/>
-      <c r="U8" s="19"/>
+      <c r="P8" s="15"/>
+      <c r="Q8" s="15"/>
+      <c r="R8" s="16"/>
+      <c r="S8" s="16"/>
+      <c r="T8" s="16"/>
+      <c r="U8" s="16"/>
       <c r="V8" s="1"/>
       <c r="W8" s="1"/>
       <c r="X8" s="1"/>
@@ -1831,29 +4224,29 @@
       <c r="AD8" s="1"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="20" t="s">
-        <v>25</v>
+      <c r="A9" s="17" t="s">
+        <v>19</v>
       </c>
-      <c r="B9" s="21"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="21"/>
-      <c r="H9" s="21"/>
-      <c r="I9" s="21"/>
-      <c r="J9" s="21"/>
-      <c r="K9" s="21"/>
-      <c r="L9" s="22"/>
-      <c r="M9" s="23"/>
-      <c r="N9" s="21"/>
-      <c r="O9" s="21"/>
-      <c r="P9" s="21"/>
-      <c r="Q9" s="21"/>
-      <c r="R9" s="21"/>
-      <c r="S9" s="21"/>
-      <c r="T9" s="21"/>
-      <c r="U9" s="22"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
+      <c r="J9" s="18"/>
+      <c r="K9" s="18"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="20"/>
+      <c r="N9" s="18"/>
+      <c r="O9" s="18"/>
+      <c r="P9" s="18"/>
+      <c r="Q9" s="18"/>
+      <c r="R9" s="18"/>
+      <c r="S9" s="18"/>
+      <c r="T9" s="18"/>
+      <c r="U9" s="19"/>
       <c r="V9" s="1"/>
       <c r="W9" s="1"/>
       <c r="X9" s="1"/>
@@ -1865,12 +4258,12 @@
       <c r="AD9" s="1"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="24"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="24"/>
-      <c r="L10" s="25"/>
-      <c r="M10" s="24"/>
-      <c r="U10" s="25"/>
+      <c r="A10" s="21"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="21"/>
+      <c r="L10" s="22"/>
+      <c r="M10" s="21"/>
+      <c r="U10" s="22"/>
       <c r="V10" s="1"/>
       <c r="W10" s="1"/>
       <c r="X10" s="1"/>
@@ -1882,12 +4275,12 @@
       <c r="AD10" s="1"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="24"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="24"/>
-      <c r="L11" s="25"/>
-      <c r="M11" s="24"/>
-      <c r="U11" s="25"/>
+      <c r="A11" s="21"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="21"/>
+      <c r="L11" s="22"/>
+      <c r="M11" s="21"/>
+      <c r="U11" s="22"/>
       <c r="V11" s="1"/>
       <c r="W11" s="1"/>
       <c r="X11" s="1"/>
@@ -1899,12 +4292,12 @@
       <c r="AD11" s="1"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="24"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="24"/>
-      <c r="L12" s="25"/>
-      <c r="M12" s="24"/>
-      <c r="U12" s="25"/>
+      <c r="A12" s="21"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="21"/>
+      <c r="L12" s="22"/>
+      <c r="M12" s="21"/>
+      <c r="U12" s="22"/>
       <c r="V12" s="1"/>
       <c r="W12" s="1"/>
       <c r="X12" s="1"/>
@@ -1916,12 +4309,12 @@
       <c r="AD12" s="1"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="24"/>
-      <c r="C13" s="25"/>
-      <c r="D13" s="24"/>
-      <c r="L13" s="25"/>
-      <c r="M13" s="24"/>
-      <c r="U13" s="25"/>
+      <c r="A13" s="21"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="21"/>
+      <c r="L13" s="22"/>
+      <c r="M13" s="21"/>
+      <c r="U13" s="22"/>
       <c r="V13" s="1"/>
       <c r="W13" s="1"/>
       <c r="X13" s="1"/>
@@ -1933,12 +4326,12 @@
       <c r="AD13" s="1"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="24"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="24"/>
-      <c r="L14" s="25"/>
-      <c r="M14" s="24"/>
-      <c r="U14" s="25"/>
+      <c r="A14" s="21"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="21"/>
+      <c r="L14" s="22"/>
+      <c r="M14" s="21"/>
+      <c r="U14" s="22"/>
       <c r="V14" s="1"/>
       <c r="W14" s="1"/>
       <c r="X14" s="1"/>
@@ -1950,12 +4343,12 @@
       <c r="AD14" s="1"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="24"/>
-      <c r="C15" s="25"/>
-      <c r="D15" s="24"/>
-      <c r="L15" s="25"/>
-      <c r="M15" s="24"/>
-      <c r="U15" s="25"/>
+      <c r="A15" s="21"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="21"/>
+      <c r="L15" s="22"/>
+      <c r="M15" s="21"/>
+      <c r="U15" s="22"/>
       <c r="V15" s="1"/>
       <c r="W15" s="1"/>
       <c r="X15" s="1"/>
@@ -1967,12 +4360,12 @@
       <c r="AD15" s="1"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="24"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="24"/>
-      <c r="L16" s="25"/>
-      <c r="M16" s="24"/>
-      <c r="U16" s="25"/>
+      <c r="A16" s="21"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="21"/>
+      <c r="L16" s="22"/>
+      <c r="M16" s="21"/>
+      <c r="U16" s="22"/>
       <c r="V16" s="1"/>
       <c r="W16" s="1"/>
       <c r="X16" s="1"/>
@@ -1984,27 +4377,27 @@
       <c r="AD16" s="1"/>
     </row>
     <row r="17" ht="42.0" customHeight="1">
-      <c r="A17" s="26"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="11"/>
-      <c r="J17" s="11"/>
-      <c r="K17" s="11"/>
-      <c r="L17" s="12"/>
-      <c r="M17" s="26"/>
-      <c r="N17" s="11"/>
-      <c r="O17" s="11"/>
-      <c r="P17" s="11"/>
-      <c r="Q17" s="11"/>
-      <c r="R17" s="11"/>
-      <c r="S17" s="11"/>
-      <c r="T17" s="11"/>
-      <c r="U17" s="12"/>
+      <c r="A17" s="23"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="10"/>
+      <c r="J17" s="10"/>
+      <c r="K17" s="10"/>
+      <c r="L17" s="11"/>
+      <c r="M17" s="23"/>
+      <c r="N17" s="10"/>
+      <c r="O17" s="10"/>
+      <c r="P17" s="10"/>
+      <c r="Q17" s="10"/>
+      <c r="R17" s="10"/>
+      <c r="S17" s="10"/>
+      <c r="T17" s="10"/>
+      <c r="U17" s="11"/>
       <c r="V17" s="1"/>
       <c r="W17" s="1"/>
       <c r="X17" s="1"/>
@@ -2016,28 +4409,28 @@
       <c r="AD17" s="1"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="27" t="s">
-        <v>26</v>
+      <c r="A18" s="24" t="s">
+        <v>20</v>
       </c>
-      <c r="C18" s="25"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="21"/>
-      <c r="I18" s="21"/>
-      <c r="J18" s="21"/>
-      <c r="K18" s="21"/>
-      <c r="L18" s="22"/>
-      <c r="M18" s="23"/>
-      <c r="N18" s="21"/>
-      <c r="O18" s="21"/>
-      <c r="P18" s="21"/>
-      <c r="Q18" s="21"/>
-      <c r="R18" s="21"/>
-      <c r="S18" s="21"/>
-      <c r="T18" s="21"/>
-      <c r="U18" s="22"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="18"/>
+      <c r="I18" s="18"/>
+      <c r="J18" s="18"/>
+      <c r="K18" s="18"/>
+      <c r="L18" s="19"/>
+      <c r="M18" s="20"/>
+      <c r="N18" s="18"/>
+      <c r="O18" s="18"/>
+      <c r="P18" s="18"/>
+      <c r="Q18" s="18"/>
+      <c r="R18" s="18"/>
+      <c r="S18" s="18"/>
+      <c r="T18" s="18"/>
+      <c r="U18" s="19"/>
       <c r="V18" s="1"/>
       <c r="W18" s="1"/>
       <c r="X18" s="1"/>
@@ -2049,12 +4442,12 @@
       <c r="AD18" s="1"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="24"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="24"/>
-      <c r="L19" s="25"/>
-      <c r="M19" s="24"/>
-      <c r="U19" s="25"/>
+      <c r="A19" s="21"/>
+      <c r="C19" s="22"/>
+      <c r="D19" s="21"/>
+      <c r="L19" s="22"/>
+      <c r="M19" s="21"/>
+      <c r="U19" s="22"/>
       <c r="V19" s="1"/>
       <c r="W19" s="1"/>
       <c r="X19" s="1"/>
@@ -2066,12 +4459,12 @@
       <c r="AD19" s="1"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="24"/>
-      <c r="C20" s="25"/>
-      <c r="D20" s="24"/>
-      <c r="L20" s="25"/>
-      <c r="M20" s="24"/>
-      <c r="U20" s="25"/>
+      <c r="A20" s="21"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="21"/>
+      <c r="L20" s="22"/>
+      <c r="M20" s="21"/>
+      <c r="U20" s="22"/>
       <c r="V20" s="1"/>
       <c r="W20" s="1"/>
       <c r="X20" s="1"/>
@@ -2083,12 +4476,12 @@
       <c r="AD20" s="1"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="24"/>
-      <c r="C21" s="25"/>
-      <c r="D21" s="24"/>
-      <c r="L21" s="25"/>
-      <c r="M21" s="24"/>
-      <c r="U21" s="25"/>
+      <c r="A21" s="21"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="21"/>
+      <c r="L21" s="22"/>
+      <c r="M21" s="21"/>
+      <c r="U21" s="22"/>
       <c r="V21" s="1"/>
       <c r="W21" s="1"/>
       <c r="X21" s="1"/>
@@ -2100,12 +4493,12 @@
       <c r="AD21" s="1"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="24"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="24"/>
-      <c r="L22" s="25"/>
-      <c r="M22" s="24"/>
-      <c r="U22" s="25"/>
+      <c r="A22" s="21"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="21"/>
+      <c r="L22" s="22"/>
+      <c r="M22" s="21"/>
+      <c r="U22" s="22"/>
       <c r="V22" s="1"/>
       <c r="W22" s="1"/>
       <c r="X22" s="1"/>
@@ -2117,12 +4510,12 @@
       <c r="AD22" s="1"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="24"/>
-      <c r="C23" s="25"/>
-      <c r="D23" s="24"/>
-      <c r="L23" s="25"/>
-      <c r="M23" s="24"/>
-      <c r="U23" s="25"/>
+      <c r="A23" s="21"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="21"/>
+      <c r="L23" s="22"/>
+      <c r="M23" s="21"/>
+      <c r="U23" s="22"/>
       <c r="V23" s="1"/>
       <c r="W23" s="1"/>
       <c r="X23" s="1"/>
@@ -2134,12 +4527,12 @@
       <c r="AD23" s="1"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="24"/>
-      <c r="C24" s="25"/>
-      <c r="D24" s="24"/>
-      <c r="L24" s="25"/>
-      <c r="M24" s="24"/>
-      <c r="U24" s="25"/>
+      <c r="A24" s="21"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="21"/>
+      <c r="L24" s="22"/>
+      <c r="M24" s="21"/>
+      <c r="U24" s="22"/>
       <c r="V24" s="1"/>
       <c r="W24" s="1"/>
       <c r="X24" s="1"/>
@@ -2151,12 +4544,12 @@
       <c r="AD24" s="1"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="24"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="24"/>
-      <c r="L25" s="25"/>
-      <c r="M25" s="24"/>
-      <c r="U25" s="25"/>
+      <c r="A25" s="21"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="21"/>
+      <c r="L25" s="22"/>
+      <c r="M25" s="21"/>
+      <c r="U25" s="22"/>
       <c r="V25" s="1"/>
       <c r="W25" s="1"/>
       <c r="X25" s="1"/>
@@ -2167,28 +4560,28 @@
       <c r="AC25" s="1"/>
       <c r="AD25" s="1"/>
     </row>
-    <row r="26" ht="113.25" customHeight="1">
-      <c r="A26" s="26"/>
-      <c r="B26" s="11"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="26"/>
-      <c r="E26" s="11"/>
-      <c r="F26" s="11"/>
-      <c r="G26" s="11"/>
-      <c r="H26" s="11"/>
-      <c r="I26" s="11"/>
-      <c r="J26" s="11"/>
-      <c r="K26" s="11"/>
-      <c r="L26" s="12"/>
-      <c r="M26" s="26"/>
-      <c r="N26" s="11"/>
-      <c r="O26" s="11"/>
-      <c r="P26" s="11"/>
-      <c r="Q26" s="11"/>
-      <c r="R26" s="11"/>
-      <c r="S26" s="11"/>
-      <c r="T26" s="11"/>
-      <c r="U26" s="12"/>
+    <row r="26" ht="164.25" customHeight="1">
+      <c r="A26" s="23"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="23"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="10"/>
+      <c r="G26" s="10"/>
+      <c r="H26" s="10"/>
+      <c r="I26" s="10"/>
+      <c r="J26" s="10"/>
+      <c r="K26" s="10"/>
+      <c r="L26" s="11"/>
+      <c r="M26" s="23"/>
+      <c r="N26" s="10"/>
+      <c r="O26" s="10"/>
+      <c r="P26" s="10"/>
+      <c r="Q26" s="10"/>
+      <c r="R26" s="10"/>
+      <c r="S26" s="10"/>
+      <c r="T26" s="10"/>
+      <c r="U26" s="11"/>
       <c r="V26" s="1"/>
       <c r="W26" s="1"/>
       <c r="X26" s="1"/>
@@ -2200,29 +4593,29 @@
       <c r="AD26" s="1"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="20" t="s">
-        <v>27</v>
+      <c r="A27" s="26" t="s">
+        <v>21</v>
       </c>
-      <c r="B27" s="21"/>
-      <c r="C27" s="22"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="21"/>
-      <c r="G27" s="21"/>
-      <c r="H27" s="21"/>
-      <c r="I27" s="21"/>
-      <c r="J27" s="21"/>
-      <c r="K27" s="21"/>
-      <c r="L27" s="22"/>
-      <c r="M27" s="23"/>
-      <c r="N27" s="21"/>
-      <c r="O27" s="21"/>
-      <c r="P27" s="21"/>
-      <c r="Q27" s="21"/>
-      <c r="R27" s="21"/>
-      <c r="S27" s="21"/>
-      <c r="T27" s="21"/>
-      <c r="U27" s="22"/>
+      <c r="B27" s="18"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="20"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="18"/>
+      <c r="G27" s="18"/>
+      <c r="H27" s="18"/>
+      <c r="I27" s="18"/>
+      <c r="J27" s="18"/>
+      <c r="K27" s="18"/>
+      <c r="L27" s="19"/>
+      <c r="M27" s="20"/>
+      <c r="N27" s="18"/>
+      <c r="O27" s="18"/>
+      <c r="P27" s="18"/>
+      <c r="Q27" s="18"/>
+      <c r="R27" s="18"/>
+      <c r="S27" s="18"/>
+      <c r="T27" s="18"/>
+      <c r="U27" s="19"/>
       <c r="V27" s="1"/>
       <c r="W27" s="1"/>
       <c r="X27" s="1"/>
@@ -2234,12 +4627,12 @@
       <c r="AD27" s="1"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="24"/>
-      <c r="C28" s="25"/>
-      <c r="D28" s="24"/>
-      <c r="L28" s="25"/>
-      <c r="M28" s="24"/>
-      <c r="U28" s="25"/>
+      <c r="A28" s="21"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="21"/>
+      <c r="L28" s="22"/>
+      <c r="M28" s="21"/>
+      <c r="U28" s="22"/>
       <c r="V28" s="1"/>
       <c r="W28" s="1"/>
       <c r="X28" s="1"/>
@@ -2251,12 +4644,12 @@
       <c r="AD28" s="1"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="24"/>
-      <c r="C29" s="25"/>
-      <c r="D29" s="24"/>
-      <c r="L29" s="25"/>
-      <c r="M29" s="24"/>
-      <c r="U29" s="25"/>
+      <c r="A29" s="21"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="21"/>
+      <c r="L29" s="22"/>
+      <c r="M29" s="21"/>
+      <c r="U29" s="22"/>
       <c r="V29" s="1"/>
       <c r="W29" s="1"/>
       <c r="X29" s="1"/>
@@ -2268,12 +4661,12 @@
       <c r="AD29" s="1"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="24"/>
-      <c r="C30" s="25"/>
-      <c r="D30" s="24"/>
-      <c r="L30" s="25"/>
-      <c r="M30" s="24"/>
-      <c r="U30" s="25"/>
+      <c r="A30" s="21"/>
+      <c r="C30" s="22"/>
+      <c r="D30" s="21"/>
+      <c r="L30" s="22"/>
+      <c r="M30" s="21"/>
+      <c r="U30" s="22"/>
       <c r="V30" s="1"/>
       <c r="W30" s="1"/>
       <c r="X30" s="1"/>
@@ -2285,12 +4678,12 @@
       <c r="AD30" s="1"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="24"/>
-      <c r="C31" s="25"/>
-      <c r="D31" s="24"/>
-      <c r="L31" s="25"/>
-      <c r="M31" s="24"/>
-      <c r="U31" s="25"/>
+      <c r="A31" s="21"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="21"/>
+      <c r="L31" s="22"/>
+      <c r="M31" s="21"/>
+      <c r="U31" s="22"/>
       <c r="V31" s="1"/>
       <c r="W31" s="1"/>
       <c r="X31" s="1"/>
@@ -2302,12 +4695,12 @@
       <c r="AD31" s="1"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="24"/>
-      <c r="C32" s="25"/>
-      <c r="D32" s="24"/>
-      <c r="L32" s="25"/>
-      <c r="M32" s="24"/>
-      <c r="U32" s="25"/>
+      <c r="A32" s="21"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="21"/>
+      <c r="L32" s="22"/>
+      <c r="M32" s="21"/>
+      <c r="U32" s="22"/>
       <c r="V32" s="1"/>
       <c r="W32" s="1"/>
       <c r="X32" s="1"/>
@@ -2319,12 +4712,12 @@
       <c r="AD32" s="1"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="24"/>
-      <c r="C33" s="25"/>
-      <c r="D33" s="24"/>
-      <c r="L33" s="25"/>
-      <c r="M33" s="24"/>
-      <c r="U33" s="25"/>
+      <c r="A33" s="21"/>
+      <c r="C33" s="22"/>
+      <c r="D33" s="21"/>
+      <c r="L33" s="22"/>
+      <c r="M33" s="21"/>
+      <c r="U33" s="22"/>
       <c r="V33" s="1"/>
       <c r="W33" s="1"/>
       <c r="X33" s="1"/>
@@ -2336,12 +4729,12 @@
       <c r="AD33" s="1"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="24"/>
-      <c r="C34" s="25"/>
-      <c r="D34" s="24"/>
-      <c r="L34" s="25"/>
-      <c r="M34" s="24"/>
-      <c r="U34" s="25"/>
+      <c r="A34" s="21"/>
+      <c r="C34" s="22"/>
+      <c r="D34" s="21"/>
+      <c r="L34" s="22"/>
+      <c r="M34" s="21"/>
+      <c r="U34" s="22"/>
       <c r="V34" s="1"/>
       <c r="W34" s="1"/>
       <c r="X34" s="1"/>
@@ -2352,28 +4745,28 @@
       <c r="AC34" s="1"/>
       <c r="AD34" s="1"/>
     </row>
-    <row r="35" ht="42.0" customHeight="1">
-      <c r="A35" s="26"/>
-      <c r="B35" s="11"/>
-      <c r="C35" s="12"/>
-      <c r="D35" s="26"/>
-      <c r="E35" s="11"/>
-      <c r="F35" s="11"/>
-      <c r="G35" s="11"/>
-      <c r="H35" s="11"/>
-      <c r="I35" s="11"/>
-      <c r="J35" s="11"/>
-      <c r="K35" s="11"/>
-      <c r="L35" s="12"/>
-      <c r="M35" s="26"/>
-      <c r="N35" s="11"/>
-      <c r="O35" s="11"/>
-      <c r="P35" s="11"/>
-      <c r="Q35" s="11"/>
-      <c r="R35" s="11"/>
-      <c r="S35" s="11"/>
-      <c r="T35" s="11"/>
-      <c r="U35" s="12"/>
+    <row r="35" ht="159.75" customHeight="1">
+      <c r="A35" s="23"/>
+      <c r="B35" s="10"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="23"/>
+      <c r="E35" s="10"/>
+      <c r="F35" s="10"/>
+      <c r="G35" s="10"/>
+      <c r="H35" s="10"/>
+      <c r="I35" s="10"/>
+      <c r="J35" s="10"/>
+      <c r="K35" s="10"/>
+      <c r="L35" s="11"/>
+      <c r="M35" s="23"/>
+      <c r="N35" s="10"/>
+      <c r="O35" s="10"/>
+      <c r="P35" s="10"/>
+      <c r="Q35" s="10"/>
+      <c r="R35" s="10"/>
+      <c r="S35" s="10"/>
+      <c r="T35" s="10"/>
+      <c r="U35" s="11"/>
       <c r="V35" s="1"/>
       <c r="W35" s="1"/>
       <c r="X35" s="1"/>
@@ -6167,9 +8560,9 @@
     <mergeCell ref="D6:G6"/>
     <mergeCell ref="H6:K6"/>
     <mergeCell ref="A9:C17"/>
+    <mergeCell ref="D9:L17"/>
     <mergeCell ref="M9:U17"/>
     <mergeCell ref="A18:C26"/>
-    <mergeCell ref="D9:L17"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
